--- a/etf_holdings/2026-10-10_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-10_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,37 +501,37 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>9821000</v>
+        <v>3645000</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,37 +546,37 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>4400000</v>
+        <v>659000</v>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -591,37 +591,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>1589000</v>
+        <v>200000</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -636,37 +636,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>2177000</v>
+        <v>196000</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -681,37 +681,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>華新</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>6362000</v>
+        <v>422000</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -726,37 +726,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>2097000</v>
+        <v>508000</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -771,37 +771,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>104000</v>
+        <v>155000</v>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -816,37 +816,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>910000</v>
+        <v>179000</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -861,37 +861,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>243000</v>
+        <v>261000</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -906,37 +906,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>126000</v>
+        <v>63000</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -951,37 +951,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>511000</v>
+        <v>1000</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -996,37 +996,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>406000</v>
+        <v>844013</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1041,37 +1041,37 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>310000</v>
+        <v>33000</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1086,37 +1086,37 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>1888000</v>
+        <v>250000</v>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1131,37 +1131,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>50000</v>
+        <v>1000000</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1176,37 +1176,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
-        <v>787000</v>
+        <v>11000</v>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1221,37 +1221,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
-        <v>11436000</v>
+        <v>99952</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1266,37 +1266,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>139000</v>
+        <v>629000</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1311,37 +1311,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>0.44%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>1304000</v>
+        <v>250000</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1356,37 +1356,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>102000</v>
+        <v>134000</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1401,37 +1401,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.66%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>278000</v>
+        <v>373000</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1446,37 +1446,37 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>189000</v>
+        <v>113000</v>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1491,37 +1491,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.63%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>18000</v>
+        <v>51000</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1536,37 +1536,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>51000</v>
+        <v>1904000</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1581,37 +1581,37 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>2.15%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>121000</v>
+        <v>429675</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1626,435 +1626,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>164000</v>
+        <v>1957000</v>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>光聖</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0.99%</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="n">
-        <v>90000</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>藥華藥</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1.22%</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="n">
-        <v>167000</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>6488</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>環球晶</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>1.23%</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="n">
-        <v>167000</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>6526</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>達發</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0.49%</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="n">
-        <v>102000</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>6531</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>愛普*</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2.03%</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="n">
-        <v>336000</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1.55%</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="n">
-        <v>114036</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>7750</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>新代</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1.17%</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="n">
-        <v>97000</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>8046</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>南電</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>1.15%</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>刪除</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>全數賣出</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="n">
-        <v>20000</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2026-10-09_00985A_full_holdings.xlsx</t>
+          <t>2026-10-09_00992A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
